--- a/pages/ParaFactorTool/Para_4year_data_road.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_road.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3512FF9A-F21E-4F4F-901C-89ED1544F87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5418BEC-00BC-4614-82CD-120D3BBF31DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="38280" yWindow="7470" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1920</definedName>
     <definedName name="Slicer_Class">#N/A</definedName>
     <definedName name="Slicer_Event">#N/A</definedName>
-    <definedName name="Slicer_Participants">#N/A</definedName>
     <definedName name="Slicer_Rank">#N/A</definedName>
     <definedName name="Slicer_Sex">#N/A</definedName>
     <definedName name="Slicer_Year">#N/A</definedName>
@@ -36,7 +35,6 @@
         <x14:slicerCache r:id="rId4"/>
         <x14:slicerCache r:id="rId5"/>
         <x14:slicerCache r:id="rId6"/>
-        <x14:slicerCache r:id="rId7"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4276,13 +4274,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>1920</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1934</xdr:row>
+      <xdr:row>1924</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4354,13 +4352,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>196</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>1933</xdr:row>
+      <xdr:row>1923</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4432,14 +4430,14 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>1920</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>1934</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>1931</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -4510,13 +4508,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>1935</xdr:row>
+      <xdr:row>1925</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>1949</xdr:row>
+      <xdr:row>1939</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4588,14 +4586,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>1935</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>1925</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>1949</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:row>1943</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -4632,84 +4630,6 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="8867775" y="3190875"/>
-              <a:ext cx="1828800" cy="2524125"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-NZ" sz="1100"/>
-                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>1935</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>1949</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-      <mc:Choice Requires="sle15">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="13" name="Participants">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0B70635-5E90-250F-B192-8AF75C75EC3E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Participants"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11068050" y="3228975"/>
               <a:ext cx="1828800" cy="2524125"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4793,35 +4713,19 @@
 </slicerCacheDefinition>
 </file>
 
-<file path=xl/slicerCaches/slicerCache6.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Participants" xr10:uid="{988D78EE-165E-4CBC-9982-02F2C1B14EDF}" sourceName="Participants">
-  <extLst>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
-      <x15:tableSlicerCache tableId="1" column="9"/>
-    </x:ext>
-  </extLst>
-</slicerCacheDefinition>
-</file>
-
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Year" xr10:uid="{16CC52F1-B0AC-4F41-A090-79E3FAACB373}" cache="Slicer_Year" caption="Year" rowHeight="241300"/>
   <slicer name="Event" xr10:uid="{429BE55C-BFBD-4D30-AC80-2857D908D9A3}" cache="Slicer_Event" caption="Event" rowHeight="241300"/>
-  <slicer name="Class" xr10:uid="{1805AA6F-5414-49B3-91A8-F2CB3649C42A}" cache="Slicer_Class" caption="Class" startItem="5" rowHeight="241300"/>
+  <slicer name="Class" xr10:uid="{1805AA6F-5414-49B3-91A8-F2CB3649C42A}" cache="Slicer_Class" caption="Class" rowHeight="241300"/>
   <slicer name="Sex" xr10:uid="{8AEA4F09-38A7-49C1-AEF1-F2EAF4FDC5DF}" cache="Slicer_Sex" caption="Sex" rowHeight="241300"/>
   <slicer name="Rank" xr10:uid="{E3D2580B-5FD9-4DDA-9681-6A304B27525B}" cache="Slicer_Rank" caption="Rank" rowHeight="241300"/>
-  <slicer name="Participants" xr10:uid="{B9673975-6F31-4B5D-B910-355B16C65F00}" cache="Slicer_Participants" caption="Participants" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C87DF06E-6799-4492-B895-FA53BE324EC9}" name="Table1" displayName="Table1" ref="A1:I1921" totalsRowCount="1" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
   <autoFilter ref="A1:I1920" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2019"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="TT"/>
@@ -4829,7 +4733,7 @@
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="C1"/>
+        <filter val="H4"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -4839,7 +4743,10 @@
     </filterColumn>
     <filterColumn colId="4">
       <filters>
-        <filter val="3"/>
+        <filter val="10"/>
+        <filter val="7"/>
+        <filter val="8"/>
+        <filter val="9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5261,7 +5168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
@@ -11051,7 +10958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197" s="7">
         <v>2019</v>
       </c>
@@ -11081,7 +10988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198" s="5">
         <v>2019</v>
       </c>
@@ -11111,7 +11018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199" s="7">
         <v>2019</v>
       </c>
@@ -22601,7 +22508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A582" s="5">
         <v>2021</v>
       </c>
@@ -38164,7 +38071,7 @@
         <v>28.4</v>
       </c>
       <c r="H1100" s="22">
-        <f t="shared" ref="H1100:H1131" si="20">G1100/(F1100*24)</f>
+        <f t="shared" ref="H1100:H1126" si="20">G1100/(F1100*24)</f>
         <v>39.347896365399713</v>
       </c>
       <c r="I1100" s="7">
@@ -49934,7 +49841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1509" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1509" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1509" s="5">
         <v>2023</v>
       </c>
@@ -49961,7 +49868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1510" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1510" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1510" s="7">
         <v>2023</v>
       </c>
@@ -49988,7 +49895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1511" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1511" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1511" s="5">
         <v>2023</v>
       </c>
@@ -59573,7 +59480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1837" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1837" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1837" s="5">
         <v>2024</v>
       </c>
@@ -59603,7 +59510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1838" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1838" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1838" s="7">
         <v>2024</v>
       </c>
@@ -59633,7 +59540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1839" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1839" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1839" s="5">
         <v>2024</v>
       </c>
@@ -59663,7 +59570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1840" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1840" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1840" s="7">
         <v>2024</v>
       </c>
@@ -62097,21 +62004,21 @@
       <c r="A1921" t="s">
         <v>1137</v>
       </c>
-      <c r="F1921" s="24" t="e">
+      <c r="F1921" s="24">
         <f>SUBTOTAL(101,Table1[Time])</f>
-        <v>#DIV/0!</v>
+        <v>2.2318055555555556E-2</v>
       </c>
       <c r="G1921" s="24">
         <f>SUBTOTAL(101,Table1[Distance])</f>
-        <v>20.8</v>
+        <v>18.672727272727276</v>
       </c>
       <c r="H1921" s="24">
         <f>SUBTOTAL(101,Table1[Speed])</f>
-        <v>30.839054565522694</v>
+        <v>32.123523719044258</v>
       </c>
       <c r="I1921" s="24">
         <f>SUBTOTAL(101,Table1[Participants])</f>
-        <v>3</v>
+        <v>9.1818181818181817</v>
       </c>
     </row>
     <row r="1922" spans="1:22" x14ac:dyDescent="0.45">
@@ -62119,24 +62026,24 @@
         <f>SUBTOTAL(107,Table1[Time])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G1922" s="24" t="e">
+      <c r="G1922" s="24">
         <f>SUBTOTAL(107,Table1[Distance])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H1922" s="24" t="e">
+        <v>1.5981807839483675</v>
+      </c>
+      <c r="H1922" s="24">
         <f>SUBTOTAL(107,Table1[Speed])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I1922" s="24" t="e">
+        <v>3.8943830658714775</v>
+      </c>
+      <c r="I1922" s="24">
         <f>SUBTOTAL(107,Table1[Participants])</f>
-        <v>#DIV/0!</v>
+        <v>0.87386289750530288</v>
       </c>
     </row>
     <row r="1923" spans="1:22" x14ac:dyDescent="0.45">
       <c r="F1923" s="2"/>
       <c r="I1923" s="24">
         <f>SUBTOTAL(102,Table1[Participants])</f>
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1924" spans="1:22" x14ac:dyDescent="0.45">

--- a/pages/ParaFactorTool/Para_4year_data_road.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_road.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5418BEC-00BC-4614-82CD-120D3BBF31DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14E8398-1FFF-432B-B53B-BBE17B9DD8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7470" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3625,7 +3625,71 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="22">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3686,44 +3750,6 @@
         <scheme val="minor"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3732,44 +3758,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3825,24 +3813,43 @@
         <scheme val="minor"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <left/>
+        <right/>
         <top style="thin">
-          <color indexed="64"/>
+          <color theme="4" tint="0.39997558519241921"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3891,45 +3898,6 @@
         <scheme val="minor"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3938,30 +3906,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -4009,30 +3953,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -4042,134 +3962,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -4274,13 +4066,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>228</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1924</xdr:row>
+      <xdr:row>606</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4352,13 +4144,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>227</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>1923</xdr:row>
+      <xdr:row>605</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4430,13 +4222,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>228</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>1931</xdr:row>
+      <xdr:row>934</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4508,13 +4300,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>1925</xdr:row>
+      <xdr:row>607</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>1939</xdr:row>
+      <xdr:row>1427</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4586,13 +4378,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>1925</xdr:row>
+      <xdr:row>607</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>1943</xdr:row>
+      <xdr:row>1431</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4724,16 +4516,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C87DF06E-6799-4492-B895-FA53BE324EC9}" name="Table1" displayName="Table1" ref="A1:I1921" totalsRowCount="1" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C87DF06E-6799-4492-B895-FA53BE324EC9}" name="Table1" displayName="Table1" ref="A1:I1921" totalsRowCount="1" headerRowDxfId="21" dataDxfId="20" tableBorderDxfId="19">
   <autoFilter ref="A1:I1920" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
     <filterColumn colId="1">
       <filters>
-        <filter val="TT"/>
+        <filter val="RR"/>
       </filters>
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="H4"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -4741,27 +4533,19 @@
         <filter val="W"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="10"/>
-        <filter val="7"/>
-        <filter val="8"/>
-        <filter val="9"/>
-      </filters>
-    </filterColumn>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{47D83299-E727-4F16-BA4C-67E7B869CE66}" name="Year" totalsRowLabel="Total" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{21F1E13E-428B-4F0F-B8C0-22FB7D371CF8}" name="Event" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{59D88B2E-B2EF-4121-AC41-833908CD74F8}" name="Class" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{1CFC19D4-6551-43DE-8714-60EBB1945876}" name="Sex" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{20A5532D-E677-4264-9AF7-364827585255}" name="Rank" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{3551F287-C639-4A37-9F44-925605FC00EF}" name="Time" totalsRowFunction="average" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{5346F5C3-AC72-472B-B4EA-7151C80D5723}" name="Distance" totalsRowFunction="average" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{BE964F66-5036-4D76-9261-56017B977C9C}" name="Speed" totalsRowFunction="average" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="1" xr3:uid="{47D83299-E727-4F16-BA4C-67E7B869CE66}" name="Year" totalsRowLabel="Total" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{21F1E13E-428B-4F0F-B8C0-22FB7D371CF8}" name="Event" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{59D88B2E-B2EF-4121-AC41-833908CD74F8}" name="Class" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{1CFC19D4-6551-43DE-8714-60EBB1945876}" name="Sex" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{20A5532D-E677-4264-9AF7-364827585255}" name="Rank" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{3551F287-C639-4A37-9F44-925605FC00EF}" name="Time" totalsRowFunction="average" dataDxfId="13" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{5346F5C3-AC72-472B-B4EA-7151C80D5723}" name="Distance" totalsRowFunction="average" dataDxfId="12" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{BE964F66-5036-4D76-9261-56017B977C9C}" name="Speed" totalsRowFunction="average" dataDxfId="11" totalsRowDxfId="1">
       <calculatedColumnFormula>G2/(F2*24)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F7B9CA07-BFFC-499C-94C1-0B0A96C21D17}" name="Participants" totalsRowFunction="average" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{F7B9CA07-BFFC-499C-94C1-0B0A96C21D17}" name="Participants" totalsRowFunction="average" dataDxfId="10" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10958,7 +10742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" s="7">
         <v>2019</v>
       </c>
@@ -10988,7 +10772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" s="5">
         <v>2019</v>
       </c>
@@ -11018,7 +10802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" s="7">
         <v>2019</v>
       </c>
@@ -11888,7 +11672,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228" s="5">
         <v>2019</v>
       </c>
@@ -11918,7 +11702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229" s="7">
         <v>2019</v>
       </c>
@@ -11948,7 +11732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230" s="5">
         <v>2019</v>
       </c>
@@ -11978,7 +11762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231" s="7">
         <v>2019</v>
       </c>
@@ -12008,7 +11792,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232" s="5">
         <v>2019</v>
       </c>
@@ -12038,7 +11822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233" s="7">
         <v>2019</v>
       </c>
@@ -12068,7 +11852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234" s="5">
         <v>2019</v>
       </c>
@@ -12098,7 +11882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235" s="7">
         <v>2019</v>
       </c>
@@ -12128,7 +11912,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236" s="5">
         <v>2019</v>
       </c>
@@ -12158,7 +11942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237" s="7">
         <v>2019</v>
       </c>
@@ -22508,7 +22292,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A582" s="5">
         <v>2021</v>
       </c>
@@ -23108,7 +22892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A602" s="5">
         <v>2021</v>
       </c>
@@ -23138,7 +22922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A603" s="7">
         <v>2021</v>
       </c>
@@ -23168,7 +22952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A604" s="5">
         <v>2021</v>
       </c>
@@ -23198,7 +22982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A605" s="7">
         <v>2021</v>
       </c>
@@ -23228,7 +23012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A606" s="5">
         <v>2021</v>
       </c>
@@ -23258,7 +23042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A607" s="7">
         <v>2021</v>
       </c>
@@ -23288,7 +23072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A608" s="5">
         <v>2021</v>
       </c>
@@ -23318,7 +23102,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A609" s="7">
         <v>2021</v>
       </c>
@@ -23348,7 +23132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A610" s="5">
         <v>2021</v>
       </c>
@@ -23378,7 +23162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A611" s="7">
         <v>2021</v>
       </c>
@@ -33038,7 +32822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A933" s="5">
         <v>2022</v>
       </c>
@@ -33065,10 +32849,10 @@
         <v>38.029150006449122</v>
       </c>
       <c r="I933" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A934" s="7">
         <v>2022</v>
       </c>
@@ -33095,10 +32879,10 @@
         <v>37.564020894381457</v>
       </c>
       <c r="I934" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A935" s="5">
         <v>2022</v>
       </c>
@@ -33125,10 +32909,10 @@
         <v>36.27014392914257</v>
       </c>
       <c r="I935" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A936" s="7">
         <v>2022</v>
       </c>
@@ -33155,10 +32939,10 @@
         <v>36.27014392914257</v>
       </c>
       <c r="I936" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A937" s="5">
         <v>2022</v>
       </c>
@@ -33185,10 +32969,10 @@
         <v>34.492278895648106</v>
       </c>
       <c r="I937" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A938" s="7">
         <v>2022</v>
       </c>
@@ -33215,10 +32999,10 @@
         <v>34.492278895648106</v>
       </c>
       <c r="I938" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A939" s="5">
         <v>2022</v>
       </c>
@@ -33245,7 +33029,7 @@
         <v>33.474114441416894</v>
       </c>
       <c r="I939" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
@@ -47411,7 +47195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1425" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1425" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1425" s="5">
         <v>2023</v>
       </c>
@@ -47441,7 +47225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1426" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1426" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1426" s="7">
         <v>2023</v>
       </c>
@@ -47471,7 +47255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1427" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1427" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1427" s="5">
         <v>2023</v>
       </c>
@@ -47501,7 +47285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1428" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1428" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1428" s="7">
         <v>2023</v>
       </c>
@@ -47531,7 +47315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1429" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1429" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1429" s="5">
         <v>2023</v>
       </c>
@@ -47561,7 +47345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1430" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1430" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1430" s="7">
         <v>2023</v>
       </c>
@@ -47591,7 +47375,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1431" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1431" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1431" s="5">
         <v>2023</v>
       </c>
@@ -47621,7 +47405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1432" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1432" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1432" s="7">
         <v>2023</v>
       </c>
@@ -47651,7 +47435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1433" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1433" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1433" s="5">
         <v>2023</v>
       </c>
@@ -47681,7 +47465,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1434" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1434" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1434" s="7">
         <v>2023</v>
       </c>
@@ -49841,7 +49625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1509" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1509" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1509" s="5">
         <v>2023</v>
       </c>
@@ -49868,7 +49652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1510" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1510" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1510" s="7">
         <v>2023</v>
       </c>
@@ -49895,7 +49679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1511" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1511" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1511" s="5">
         <v>2023</v>
       </c>
@@ -59480,7 +59264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1837" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1837" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1837" s="5">
         <v>2024</v>
       </c>
@@ -59510,7 +59294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1838" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1838" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1838" s="7">
         <v>2024</v>
       </c>
@@ -59540,7 +59324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1839" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1839" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1839" s="5">
         <v>2024</v>
       </c>
@@ -59570,7 +59354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1840" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1840" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1840" s="7">
         <v>2024</v>
       </c>
@@ -61760,7 +61544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1913" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1913" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1913" s="5">
         <v>2024</v>
       </c>
@@ -61787,10 +61571,10 @@
         <v>35.596544478169513</v>
       </c>
       <c r="I1913" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1914" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1914" s="7">
         <v>2024</v>
       </c>
@@ -61817,10 +61601,10 @@
         <v>35.254942767950055</v>
       </c>
       <c r="I1914" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1915" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1915" s="5">
         <v>2024</v>
       </c>
@@ -61847,10 +61631,10 @@
         <v>35.189844200807848</v>
       </c>
       <c r="I1915" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1916" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1916" s="7">
         <v>2024</v>
       </c>
@@ -61877,10 +61661,10 @@
         <v>34.935838680109988</v>
       </c>
       <c r="I1916" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1917" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1917" s="5">
         <v>2024</v>
       </c>
@@ -61907,10 +61691,10 @@
         <v>34.935838680109988</v>
       </c>
       <c r="I1917" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1918" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1918" s="7">
         <v>2024</v>
       </c>
@@ -61937,10 +61721,10 @@
         <v>33.981945837512541</v>
       </c>
       <c r="I1918" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1919" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1919" s="5">
         <v>2024</v>
       </c>
@@ -61967,10 +61751,10 @@
         <v>33.711442786069654</v>
       </c>
       <c r="I1919" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1920" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1920" s="4">
         <v>2024</v>
       </c>
@@ -61997,7 +61781,7 @@
         <v>33.441544198289101</v>
       </c>
       <c r="I1920" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1921" spans="1:22" x14ac:dyDescent="0.45">
@@ -62006,44 +61790,44 @@
       </c>
       <c r="F1921" s="24">
         <f>SUBTOTAL(101,Table1[Time])</f>
-        <v>2.2318055555555556E-2</v>
+        <v>0.1049845679012346</v>
       </c>
       <c r="G1921" s="24">
         <f>SUBTOTAL(101,Table1[Distance])</f>
-        <v>18.672727272727276</v>
+        <v>85.619999999999976</v>
       </c>
       <c r="H1921" s="24">
         <f>SUBTOTAL(101,Table1[Speed])</f>
-        <v>32.123523719044258</v>
+        <v>37.266298888299573</v>
       </c>
       <c r="I1921" s="24">
         <f>SUBTOTAL(101,Table1[Participants])</f>
-        <v>9.1818181818181817</v>
+        <v>12.955555555555556</v>
       </c>
     </row>
     <row r="1922" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="F1922" s="24" t="e">
+      <c r="F1922" s="24">
         <f>SUBTOTAL(107,Table1[Time])</f>
-        <v>#DIV/0!</v>
+        <v>3.1798126033029993E-3</v>
       </c>
       <c r="G1922" s="24">
         <f>SUBTOTAL(107,Table1[Distance])</f>
-        <v>1.5981807839483675</v>
+        <v>8.4835294970473623</v>
       </c>
       <c r="H1922" s="24">
         <f>SUBTOTAL(107,Table1[Speed])</f>
-        <v>3.8943830658714775</v>
+        <v>1.8301930323183966</v>
       </c>
       <c r="I1922" s="24">
         <f>SUBTOTAL(107,Table1[Participants])</f>
-        <v>0.87386289750530288</v>
+        <v>3.9655078521234244</v>
       </c>
     </row>
     <row r="1923" spans="1:22" x14ac:dyDescent="0.45">
       <c r="F1923" s="2"/>
       <c r="I1923" s="24">
         <f>SUBTOTAL(102,Table1[Participants])</f>
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1924" spans="1:22" x14ac:dyDescent="0.45">
@@ -62179,24 +61963,24 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A21:E1920 A1922:E1996">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$E21&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$E21&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$E21&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:F20 F21:F69">
-    <cfRule type="expression" dxfId="2" priority="136">
+    <cfRule type="expression" dxfId="6" priority="136">
       <formula>$E2&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="137">
+    <cfRule type="expression" dxfId="5" priority="137">
       <formula>$E2&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="138">
+    <cfRule type="expression" dxfId="4" priority="138">
       <formula>$E2&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
